--- a/Dashboards/data/Data final/ingresos/inglab_edad.xlsx
+++ b/Dashboards/data/Data final/ingresos/inglab_edad.xlsx
@@ -1339,7 +1339,7 @@
         <v>2021</v>
       </c>
       <c r="C70" t="n">
-        <v>152.22</v>
+        <v>133.25</v>
       </c>
     </row>
     <row r="71">
@@ -1352,7 +1352,7 @@
         <v>2021</v>
       </c>
       <c r="C71" t="n">
-        <v>374.62</v>
+        <v>368.37</v>
       </c>
     </row>
     <row r="72">
@@ -1365,7 +1365,7 @@
         <v>2021</v>
       </c>
       <c r="C72" t="n">
-        <v>483.25</v>
+        <v>481.85</v>
       </c>
     </row>
     <row r="73">
@@ -1378,7 +1378,7 @@
         <v>2021</v>
       </c>
       <c r="C73" t="n">
-        <v>258.03</v>
+        <v>278.61</v>
       </c>
     </row>
     <row r="74">
@@ -1391,7 +1391,7 @@
         <v>2022</v>
       </c>
       <c r="C74" t="n">
-        <v>141.18</v>
+        <v>162.35</v>
       </c>
     </row>
     <row r="75">
@@ -1404,7 +1404,7 @@
         <v>2022</v>
       </c>
       <c r="C75" t="n">
-        <v>386.4</v>
+        <v>391.23</v>
       </c>
     </row>
     <row r="76">
@@ -1417,7 +1417,7 @@
         <v>2022</v>
       </c>
       <c r="C76" t="n">
-        <v>508.98</v>
+        <v>516.13</v>
       </c>
     </row>
     <row r="77">
@@ -1430,7 +1430,7 @@
         <v>2022</v>
       </c>
       <c r="C77" t="n">
-        <v>281.01</v>
+        <v>310.89</v>
       </c>
     </row>
     <row r="78">
@@ -1443,7 +1443,7 @@
         <v>2023</v>
       </c>
       <c r="C78" t="n">
-        <v>129.32</v>
+        <v>148.23</v>
       </c>
     </row>
     <row r="79">
@@ -1456,7 +1456,7 @@
         <v>2023</v>
       </c>
       <c r="C79" t="n">
-        <v>386.14</v>
+        <v>373.46</v>
       </c>
     </row>
     <row r="80">
@@ -1469,7 +1469,7 @@
         <v>2023</v>
       </c>
       <c r="C80" t="n">
-        <v>512.66</v>
+        <v>510.15</v>
       </c>
     </row>
     <row r="81">
@@ -1482,7 +1482,7 @@
         <v>2023</v>
       </c>
       <c r="C81" t="n">
-        <v>281</v>
+        <v>290.98</v>
       </c>
     </row>
     <row r="82">
@@ -1495,7 +1495,7 @@
         <v>2024</v>
       </c>
       <c r="C82" t="n">
-        <v>129.62</v>
+        <v>174.13</v>
       </c>
     </row>
     <row r="83">
@@ -1508,7 +1508,7 @@
         <v>2024</v>
       </c>
       <c r="C83" t="n">
-        <v>386.44</v>
+        <v>382.89</v>
       </c>
     </row>
     <row r="84">
@@ -1521,7 +1521,7 @@
         <v>2024</v>
       </c>
       <c r="C84" t="n">
-        <v>504.76</v>
+        <v>488.81</v>
       </c>
     </row>
     <row r="85">
@@ -1534,7 +1534,7 @@
         <v>2024</v>
       </c>
       <c r="C85" t="n">
-        <v>364.94</v>
+        <v>291.6</v>
       </c>
     </row>
     <row r="86">
@@ -1547,7 +1547,7 @@
         <v>2025</v>
       </c>
       <c r="C86" t="n">
-        <v>132.45</v>
+        <v>141.49</v>
       </c>
     </row>
     <row r="87">
@@ -1560,7 +1560,7 @@
         <v>2025</v>
       </c>
       <c r="C87" t="n">
-        <v>421.58</v>
+        <v>436.95</v>
       </c>
     </row>
     <row r="88">
@@ -1573,7 +1573,7 @@
         <v>2025</v>
       </c>
       <c r="C88" t="n">
-        <v>530.52</v>
+        <v>570.34</v>
       </c>
     </row>
     <row r="89">
@@ -1586,7 +1586,7 @@
         <v>2025</v>
       </c>
       <c r="C89" t="n">
-        <v>306.59</v>
+        <v>328.29</v>
       </c>
     </row>
   </sheetData>
